--- a/pricing/商务成品/对外/定制报价/Trinity模型报价表_OpenAI定制.xlsx
+++ b/pricing/商务成品/对外/定制报价/Trinity模型报价表_OpenAI定制.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="仅有折扣" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="仅有折扣" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +46,24 @@
       <name val="Menlo"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="PingFang SC"/>
+      <color rgb="00713F12"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <color rgb="001D2939"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -65,8 +82,14 @@
         <bgColor rgb="FFE8F4FC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF3C7"/>
+        <bgColor rgb="FFFEF3C7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -121,12 +144,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D5DD"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D5DD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D5DD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D5DD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyFill="1" applyFont="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -507,6 +556,80 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="48" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>本页为 OpenAI 定制表累积更新日志（新→旧），供 Trinity 对内核对；外发客户前可删本页。重建：pricing/scripts/build_openai_custom_quote.py。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>分类</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>更新说明</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2026.9.20</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>OpenAI定制</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>启用「更新」累积日志；本轮 4 款</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>定制表 · 首启</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -523,251 +646,251 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Trinity · 折扣报价表</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>模态</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>厂商</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>模型 ID</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>显示名</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>刊例价·输入</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>刊例价·输出</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>刊例价·缓存</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>对外·≥$5k</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>对外·≥$10k</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>对外·≥$50k</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>生文</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>gpt-5.6-sol</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>GPT-5.6 Sol</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>30.00</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>0.50</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>8.5折</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>8.2折</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>7.2折</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="n"/>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="A4" s="10" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>gpt-5.6-terra</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>GPT-5.6 Terra</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>12.00</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>0.20</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="9" t="inlineStr">
         <is>
           <t>8.5折</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>8.2折</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="9" t="inlineStr">
         <is>
           <t>7.2折</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="A5" s="11" t="n"/>
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>GPT-5.6 Luna</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>0.20</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>1.20</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>6.2折</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>6折</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>5.5折</t>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>8.5折</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>8.2折</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>7.2折</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>生图</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>gpt-image-2</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>GPT Image 2</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>入 5.00 · 出 30.00 · 缓 1.25</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>8.5折</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>8.2折</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>7.2折</t>
         </is>
